--- a/reference/datasheets/E77-400MBL-01-PIN.xlsx
+++ b/reference/datasheets/E77-400MBL-01-PIN.xlsx
@@ -7,7 +7,10 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="E77-400MBL-01" sheetId="2" r:id="rId1"/>
+    <sheet name="E77+INMP441+MAX98357" sheetId="4" r:id="rId1"/>
+    <sheet name="E77-400MBL-01" sheetId="2" r:id="rId2"/>
+    <sheet name="INMP441 + MAX98357" sheetId="3" r:id="rId3"/>
+    <sheet name="STM32WLE5" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +30,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="334">
+  <si>
+    <t>E77-400MBL-01</t>
+  </si>
+  <si>
+    <t>INMP441</t>
+  </si>
   <si>
     <t>引脚序号</t>
   </si>
@@ -35,15 +44,124 @@
     <t>定义</t>
   </si>
   <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>连接引脚</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PA8</t>
+  </si>
+  <si>
+    <t>SPI2_SCK / I2S2_CK</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>串行时钟 (Serial Clock / BCLK)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>PA9</t>
+  </si>
+  <si>
+    <t>SPI2_NSS / I2S2_WS</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>字选择信号 / 帧同步 (Word Select / LRCLK)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>PA10</t>
+  </si>
+  <si>
+    <t>SPI2_MOSI / I2S2_SD</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>串行数据输出 (Serial Data Output)</t>
+  </si>
+  <si>
+    <t>1/18</t>
+  </si>
+  <si>
+    <t>3.3V</t>
+  </si>
+  <si>
+    <t>VDD</t>
+  </si>
+  <si>
+    <t>电源引脚 (Power Supply)</t>
+  </si>
+  <si>
+    <t>6/17</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>L/R/GND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/R接GND (低电平)：配置为左声道 </t>
+  </si>
+  <si>
+    <t>MAX98357</t>
+  </si>
+  <si>
+    <t>BCLK</t>
+  </si>
+  <si>
+    <t>位时钟 (Bit Clock)</t>
+  </si>
+  <si>
+    <t>LRCLK</t>
+  </si>
+  <si>
+    <t>左右声道时钟 (Left/Right Clock)也常被称为 WS (Word Select)。</t>
+  </si>
+  <si>
+    <t>DIN</t>
+  </si>
+  <si>
+    <t>数字音频输入 (Digital Data In)</t>
+  </si>
+  <si>
+    <t>SD/VDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD直接接VDD输出左声道
+</t>
+  </si>
+  <si>
+    <t>接地引脚 (Ground)</t>
+  </si>
+  <si>
+    <t>GAIN</t>
+  </si>
+  <si>
+    <t>增益选择 (Gain Select)，悬空为默认增益（9dB或12dB，视版本而定）</t>
+  </si>
+  <si>
     <t>复用功能（Alternate Functions）</t>
   </si>
   <si>
     <t>附加功能（Additional functions）</t>
   </si>
   <si>
-    <t>3.3V</t>
-  </si>
-  <si>
     <t>3.3V供电引出脚</t>
   </si>
   <si>
@@ -71,9 +189,6 @@
     <t>MCU的SWDIO引脚</t>
   </si>
   <si>
-    <t>GND</t>
-  </si>
-  <si>
     <t>底板参考地</t>
   </si>
   <si>
@@ -116,9 +231,6 @@
     <t>TIM1_BKIN, I2C3_SMBA, SPI2_NSS/I2S2_WS, LPUART1_RTS, CM4_EVENTOUT</t>
   </si>
   <si>
-    <t>PA10</t>
-  </si>
-  <si>
     <t>RTC_REFIN, TIM1_CH3, I2C1_SDA, SPI2_MOSI/I2S2_SD, USART1_RX, DEBUG_RF_HSE32RDY, TIM17_BKIN, CM4_EVENTOUT</t>
   </si>
   <si>
@@ -143,15 +255,9 @@
     <t>ADC_IN8</t>
   </si>
   <si>
-    <t>PA9</t>
-  </si>
-  <si>
     <t>TIM1_CH2, SPI2_NSS/I2S2_WS, I2C1_SCL, SPI2_SCK/I2S2_CK, USART1_TX, CM4_EVENTOUT</t>
   </si>
   <si>
-    <t>PA8</t>
-  </si>
-  <si>
     <t>MCO, TIM1_CH1, SPI2_SCK/I2S2_CK, USART1_CK, LPTIM2_OUT, CM4_EVENTOUT</t>
   </si>
   <si>
@@ -234,6 +340,717 @@
   </si>
   <si>
     <t>TIM2_CH1, TIM2_ETR, SPI2_MISO, SPI1_SCK, DEBUG_SUBGHZSPI_SCKOUT, LPTIM2_ETR, CM4_EVENTOUT</t>
+  </si>
+  <si>
+    <t>INMP441麦克风模块</t>
+  </si>
+  <si>
+    <t>L/R</t>
+  </si>
+  <si>
+    <t>声道选择引脚 (Left/Right Select)（不能悬空）
+这是一个配置引脚，用于决定该麦克风在I²S数据流中占据哪个声道。通常：
+• 接GND (低电平)：配置为左声道 (Left Channel)
+• 接VDD (高电平)：配置为右声道 (Right Channel)</t>
+  </si>
+  <si>
+    <t>接地引脚 (Ground)
+电源地线，必须连接到系统的地。</t>
+  </si>
+  <si>
+    <t>字选择信号 / 帧同步 (Word Select / LRCLK)
+这是I²S协议中的关键信号线，用于区分左右声道的数据帧。
+• 低电平：表示正在传输左声道数据。
+• 高电平：表示正在传输右声道数据。</t>
+  </si>
+  <si>
+    <t>电源引脚 (Power Supply)
+供电电压范围通常为 1.8V 至 3.3V。注意不要接5V，否则会烧毁模块。</t>
+  </si>
+  <si>
+    <t>串行时钟 (Serial Clock / BCLK)
+位时钟信号，由主控提供，同步数据的传输。数据在SCK的上升沿或下降沿被采样。</t>
+  </si>
+  <si>
+    <t>串行数据输出 (Serial Data Output)
+麦克风采集到的数字音频数据通过这根线输出给主控芯片。数据格式通常为24位或32位。</t>
+  </si>
+  <si>
+    <t>MAX98357功放模块</t>
+  </si>
+  <si>
+    <t>电源正极 (Power Supply)
+输入电压范围通常为 2.5V 至 5.5V。建议使用5V供电以获得更大功率，也可以使用3.3V供电。</t>
+  </si>
+  <si>
+    <t>关机与声道选择 (Shutdown &amp; Channel Select)
+这是一个多功能配置引脚：
+• 拉低 (接GND)：功放进入关机模式 (Shutdown)，几乎不耗电。
+• 悬空/上拉：根据电压分压决定输出左声道、右声道或立体声混合 (Mono)。通常直接接VDD输出左声道或混合声道。</t>
+  </si>
+  <si>
+    <t>增益选择 (Gain Select)
+用于设置放大器的输出增益（音量大小）。通过连接电阻在GAIN与GND/VDD之间，可配置3dB至15dB不等的增益。通常悬空为默认增益（9dB或12dB，视版本而定）。</t>
+  </si>
+  <si>
+    <t>数字音频输入 (Digital Data In)
+I²S协议的数据输入线。连接到麦克风（如INMP441）或解码芯片的SD（数据输出）引脚。</t>
+  </si>
+  <si>
+    <t>位时钟 (Bit Clock)
+I²S协议的位同步时钟。必须连接到主控芯片（如ESP32）的BCLK引脚。</t>
+  </si>
+  <si>
+    <t>左右声道时钟 (Left/Right Clock)
+也常被称为 WS (Word Select)。用于同步左右声道的切换。连接到主控芯片的LRCLK/WS引脚。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin number (UFQFPN48) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pin number (UFBGA73) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pin name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pin type </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I/O structure </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Notes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alternate functions </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Additional functions</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VSS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> S </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I/O </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FT_a </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JTD0/TRACESWO, TIM2_CH2, SPI1_SCK, RF_IRQ0, USART1_RTS, DEBUG_RF_DT81, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_INM, COMP2_INM, ADC_IN2, TAMP_IN3/WKUP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FT_fa </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NJTRST, I2C3_SDA, SPI1_MISO, USART1_CTS, DEBUG_RF_LDORDY, TIM17_BKIN, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_INP, COMP2_INP, ADC_IN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_IN1, I2C1_SMBA, SPI1_MOSI, RF_IRQ1, USART1_CK, COMP2_OUT, TIM16_BKIN, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDD </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FT_f </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_ETR, I2C1_SCL, USART1_TX, TIM16_CH1N, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_IN2, TIM1_BKIN, I2C1_SDA, USART1_RX, TIM17_CH1N, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH2N, I2C1_SCL, RF_IRQ2, TIM16_CH1, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH3N, I2C1_SDA, SPI2_NSS/I2S2_WS, IR_OUT, TIM17_CH1, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_IN1, I2C3_SCL, LPUART1_RX, LPTIM2_IN1, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_OUT, SPI2_MOSI/I2S2_SD, I2C3_SDA, LPUART1_TX, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_IN2, SPI2_MISO, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_ETR, SPI2_MOSI/I2S2_SD, LPTIM2_ETR, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I2S2_MCK, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM2_CH1, I2C3_SMBA, I2S_CKIN, USART2_CTS, COMP1_OUT, DEBUG_PWR_REGLP1S, TIM2_ETR, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TAMP_IN2/WKUP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM2_CH2, LPTIM3_OUT, I2C1_SMBA, SPI1_SCK, USART2_RTS, LPUART1_RTS, DEBUG_PWR_REGLP2S, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LSCO, TIM2_CH3, USART2_TX, LPUART1_TX, COMP2_OUT, DEBUG_PWR_LDORDY, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LSCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM2_CH4, I2S2_MCK, USART2_RX, LPUART1_RX, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RTC_OUT2, LPTIM1_OUT, SPI1_NSS, USART2_CK, DEBUG_SUBGHZSPI_NSSOUT, LPTIM2_OUT, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM2_CH1, TIM2_ETR, SPI2_MISO, SPI1_SCK, DEBUG_SUBGHZSPI_SCKOUT, LPTIM2_ETR, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_BKIN, I2C2_SMBA, SPI1_MISO, LPUART1_CTS, DEBUG_SUBGHZSPI_MISCOUT, TIM16_CH1, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH1N, I2C3_SCL, SPI1_MOSI, COMP2_OUT, DEBUG_SUBGHZSPI_MOSIOUT, TIM17_CH1, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MCO, TIM1_CH1, SPI2_SCK/I2S2_CK, USART1_CK, LPTIM2_OUT, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH2, SPI2_NSS/I2S2_WS, I2C1_SCL, SPI2_SCK/I2S2_CK, USART1_TX, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM2_CH3, I2C3_SCL, SPI2_SCK/I2S2_CK, LPUART1_RX, COMP1_OUT, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM2_CH4, I2C3_SDA, LPUART1_TX, COMP2_OUT, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NRST </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PH3-BOOT0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BOOT0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VSSRF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RFLP </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RFLN </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RFQ_LP </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> O </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> J9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RFQ_HP </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VR_PA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDDPA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OSC_IN </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OSC_OUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDDRF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDDRF1V55 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB0-VDD_TCXO </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_OUT, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPUART1_RTS_DE, LPTIM2_IN1, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP2_INP, ADC_IN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LPTIM1_OUT, I2C3_SMBA, SPI1_NSS, DEBUG_RF_SMPSRDY, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_INP, COMP2_INM, ADC_IN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_BKIN, I2C3_SMBA, SPI2_NSS/I2S2_WS, LPUART1_RTS, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH1N, I2C3_SCL, SPI2_SCK/I2S2_CK, LPUART1_CTS, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADC_IN0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH2N, I2S2_MCK, I2C3_SDA, SPI2_MISO, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADC_IN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RTC_REFIN, TIM1_CH3, I2C1_SDA, SPI2_MOSI/I2S2_SD, USART1_RX, DEBUG_RF_HSE32RDY, TIM17_BKIN, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_INM, COMP2_INM, DAC_OUT1, ADC_IN6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH4, TIM1_BKIN2, LPTIM3_ETR, I2C2_SDA, SPI1_MISO, USART1_CTS, DEBUG_RF_NRESET, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_INM, COMP2_INM, ADC_IN7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_ETR, LPTIM3_IN1, I2C2_SCL, SPI1_MOSI, RF_BUSY, USART1_RTS, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADC_IN8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JTMS-SWDIO, I2C2_SMBA, IR_OUT, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADC_IN9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VBAT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (1)(2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TAMP_IN1/RTC_OUT1/RTC_TS/WKUP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC14-OSC32_IN </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OSC32_IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PC15-OSC32_OUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OSC32_OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VREF+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JTCK-SWCLK, LPTIM1_OUT, I2C1_SMBA, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADC_IN10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PA15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JTDI, TIM2_CH1, TIM2_ETR, I2C2_SDA, SPI1_NSS, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COMP1_INM, COMP2_INP, ADC_IN11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PB15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TIM1_CH3N, I2C2_SCL, SPI2_MOSI/I2S2_SD, CM4_EVENTOUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VFBSMPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VDDSMPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VLXSMPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VSSSMPS </t>
   </si>
 </sst>
 </file>
@@ -246,8 +1063,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -620,7 +1445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -638,7 +1463,35 @@
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -651,7 +1504,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -660,13 +1513,28 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -678,7 +1546,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -689,7 +1559,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -699,10 +1571,27 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -718,7 +1607,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -731,7 +1620,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -740,13 +1629,28 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -755,10 +1659,32 @@
       <left style="medium">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
@@ -771,7 +1697,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
@@ -784,6 +1710,162 @@
         <color auto="1"/>
       </left>
       <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -912,141 +1994,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="17">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="35">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="16">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="36">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="18">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="35">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="37">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1055,35 +2140,143 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1396,406 +2589,3125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="B2:F17"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="9.90909090909091" customWidth="1"/>
+    <col min="4" max="4" width="26.3636363636364" customWidth="1"/>
+    <col min="5" max="5" width="13.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="72.5454545454545" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" customHeight="1" spans="2:6">
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" customHeight="1" spans="2:6">
+      <c r="B3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="2:6">
+      <c r="B4" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:6">
+      <c r="B5" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:6">
+      <c r="B6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:6">
+      <c r="B7" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="41"/>
+      <c r="E7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:6">
+      <c r="B8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="44"/>
+      <c r="E8" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:6">
+      <c r="B10" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" customHeight="1" spans="2:6">
+      <c r="B11" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:6">
+      <c r="B12" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:6">
+      <c r="B13" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:6">
+      <c r="B14" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:6">
+      <c r="B15" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:6">
+      <c r="B16" s="48">
+        <v>46190</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:6">
+      <c r="B17" s="49">
+        <v>46190</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="50"/>
+      <c r="E17" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B2:E32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="16.4545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.0909090909091" style="1" customWidth="1"/>
-    <col min="4" max="4" width="118.909090909091" style="1" customWidth="1"/>
-    <col min="5" max="5" width="54" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.4545454545455" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.0909090909091" style="2" customWidth="1"/>
+    <col min="4" max="4" width="118.909090909091" style="2" customWidth="1"/>
+    <col min="5" max="5" width="54" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="50" customHeight="1" spans="2:5">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:5">
+      <c r="B3" s="34">
         <v>1</v>
       </c>
+      <c r="C3" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" customHeight="1" spans="2:5">
+      <c r="B4" s="26">
+        <v>2</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5" customHeight="1" spans="2:5">
+      <c r="B5" s="26">
+        <v>3</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6" customHeight="1" spans="2:5">
+      <c r="B6" s="26">
+        <v>4</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7" customHeight="1" spans="2:5">
+      <c r="B7" s="26">
+        <v>5</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="36"/>
+    </row>
+    <row r="8" customHeight="1" spans="2:5">
+      <c r="B8" s="26">
+        <v>6</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="36"/>
+    </row>
+    <row r="9" customHeight="1" spans="2:5">
+      <c r="B9" s="26">
+        <v>7</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:5">
+      <c r="B10" s="26">
+        <v>8</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:5">
+      <c r="B11" s="26">
+        <v>9</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12" customHeight="1" spans="2:5">
+      <c r="B12" s="26">
+        <v>10</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:5">
+      <c r="B13" s="26">
+        <v>11</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14" customHeight="1" spans="2:5">
+      <c r="B14" s="26">
+        <v>12</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:5">
+      <c r="B15" s="26">
+        <v>13</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:5">
+      <c r="B16" s="26">
+        <v>14</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:5">
+      <c r="B17" s="26">
+        <v>15</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="36"/>
+    </row>
+    <row r="18" customHeight="1" spans="2:5">
+      <c r="B18" s="26">
+        <v>16</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="36"/>
+    </row>
+    <row r="19" customHeight="1" spans="2:5">
+      <c r="B19" s="26">
+        <v>17</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="36"/>
+    </row>
+    <row r="20" customHeight="1" spans="2:5">
+      <c r="B20" s="26">
+        <v>18</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="36"/>
+    </row>
+    <row r="21" customHeight="1" spans="2:5">
+      <c r="B21" s="26">
+        <v>19</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="36"/>
+    </row>
+    <row r="22" customHeight="1" spans="2:5">
+      <c r="B22" s="26">
+        <v>20</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="36"/>
+    </row>
+    <row r="23" customHeight="1" spans="2:5">
+      <c r="B23" s="26">
+        <v>21</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:5">
+      <c r="B24" s="26">
+        <v>22</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:5">
+      <c r="B25" s="26">
+        <v>23</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="36"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:5">
+      <c r="B26" s="26">
+        <v>24</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="36"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:5">
+      <c r="B27" s="26">
+        <v>25</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="36"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:5">
+      <c r="B28" s="26">
+        <v>26</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="36"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:5">
+      <c r="B29" s="26">
+        <v>27</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="2:5">
+      <c r="B30" s="26">
+        <v>28</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="36"/>
+    </row>
+    <row r="31" customHeight="1" spans="2:5">
+      <c r="B31" s="26">
+        <v>29</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="36"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:5">
+      <c r="B32" s="29">
+        <v>30</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:D19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="11.7272727272727" customWidth="1"/>
+    <col min="3" max="3" width="14.2727272727273" customWidth="1"/>
+    <col min="4" max="4" width="76.6363636363636" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" customHeight="1" spans="2:4">
+      <c r="B2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+    </row>
+    <row r="3" customHeight="1" spans="2:4">
+      <c r="B3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="60" spans="2:4">
+      <c r="B4" s="23">
+        <v>1</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1" spans="2:4">
+      <c r="B5" s="26">
+        <v>2</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" ht="60" spans="2:4">
+      <c r="B6" s="26">
+        <v>3</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" ht="43" customHeight="1" spans="2:4">
+      <c r="B7" s="26">
+        <v>4</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" ht="45" spans="2:4">
+      <c r="B8" s="26">
+        <v>5</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" ht="45.75" spans="2:4">
+      <c r="B9" s="29">
+        <v>6</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:4">
+      <c r="B11" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+    </row>
+    <row r="12" customHeight="1" spans="2:4">
+      <c r="B12" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1" spans="2:4">
+      <c r="B13" s="23">
+        <v>1</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" ht="37" customHeight="1" spans="2:4">
+      <c r="B14" s="26">
+        <v>2</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" ht="75" spans="2:4">
+      <c r="B15" s="26">
+        <v>3</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" ht="60" spans="2:4">
+      <c r="B16" s="26">
+        <v>4</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" ht="45" spans="2:4">
+      <c r="B17" s="26">
+        <v>5</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" ht="30" spans="2:4">
+      <c r="B18" s="26">
+        <v>6</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" ht="45.75" spans="2:4">
+      <c r="B19" s="29">
+        <v>7</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B11:D11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:I87"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="12.6363636363636" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.1818181818182" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.5454545454545" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.8181818181818" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="107" style="2" customWidth="1"/>
+    <col min="9" max="9" width="51.1818181818182" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" s="1" customFormat="1" ht="50" customHeight="1" spans="2:9">
+      <c r="B2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="D2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:9">
+      <c r="B3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:9">
+      <c r="B4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:9">
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:9">
+      <c r="B6" s="9">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C6" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:9">
+      <c r="B7" s="9">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customHeight="1" spans="2:5">
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="C7" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:9">
+      <c r="B8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:9">
+      <c r="B9" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:9">
+      <c r="B10" s="9">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="C10" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:9">
+      <c r="B11" s="9">
         <v>5</v>
       </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" customHeight="1" spans="2:5">
-      <c r="B4" s="8">
-        <v>2</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="C11" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:9">
+      <c r="B12" s="9">
         <v>6</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="C12" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:9">
+      <c r="B13" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:9">
+      <c r="B14" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:9">
+      <c r="B15" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:9">
+      <c r="B16" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:9">
+      <c r="B17" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:9">
+      <c r="B18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:9">
+      <c r="B19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:9">
+      <c r="B20" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:9">
+      <c r="B21" s="9">
         <v>7</v>
       </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" customHeight="1" spans="2:5">
-      <c r="B5" s="8">
-        <v>3</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="C21" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:9">
+      <c r="B22" s="9">
         <v>8</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="C22" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:9">
+      <c r="B23" s="9">
         <v>9</v>
       </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" customHeight="1" spans="2:5">
-      <c r="B6" s="8">
-        <v>4</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="C23" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:9">
+      <c r="B24" s="9">
         <v>10</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="C24" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:9">
+      <c r="B25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:9">
+      <c r="B26" s="9">
         <v>11</v>
       </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" customHeight="1" spans="2:5">
-      <c r="B7" s="8">
-        <v>5</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="C26" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:9">
+      <c r="B27" s="9">
         <v>12</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="C27" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:9">
+      <c r="B28" s="9">
         <v>13</v>
       </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" customHeight="1" spans="2:5">
-      <c r="B8" s="8">
-        <v>6</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="C28" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="2:9">
+      <c r="B29" s="9">
         <v>14</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="C29" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="2:9">
+      <c r="B30" s="9">
         <v>15</v>
       </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" customHeight="1" spans="2:5">
-      <c r="B9" s="8">
-        <v>7</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="C30" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="2:9">
+      <c r="B31" s="9">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="C31" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="2:9">
+      <c r="B32" s="9">
         <v>17</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="C32" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="2:9">
+      <c r="B33" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="2:9">
+      <c r="B34" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="2:9">
+      <c r="B35" s="9">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="2:5">
-      <c r="B10" s="8">
-        <v>8</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="C35" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="2:9">
+      <c r="B36" s="9">
         <v>19</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="C36" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="2:9">
+      <c r="B37" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="2:9">
+      <c r="B38" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="2:9">
+      <c r="B39" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="2:9">
+      <c r="B40" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="2:9">
+      <c r="B41" s="9">
         <v>20</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="C41" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:9">
+      <c r="B42" s="9">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="2:5">
-      <c r="B11" s="8">
-        <v>9</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="C42" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:9">
+      <c r="B43" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:9">
+      <c r="B44" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:9">
+      <c r="B45" s="9">
         <v>22</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="C45" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:9">
+      <c r="B46" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="2:9">
+      <c r="B47" s="9">
         <v>23</v>
       </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" customHeight="1" spans="2:5">
-      <c r="B12" s="8">
-        <v>10</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="C47" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="2:9">
+      <c r="B48" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="2:9">
+      <c r="B49" s="9">
         <v>24</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="C49" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="2:9">
+      <c r="B50" s="9">
         <v>25</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="C50" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="2:9">
+      <c r="B51" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="2:9">
+      <c r="B52" s="9">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="2:5">
-      <c r="B13" s="8">
-        <v>11</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="C52" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="2:9">
+      <c r="B53" s="9">
         <v>27</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="C53" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="2:9">
+      <c r="B54" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="2:9">
+      <c r="B55" s="9">
         <v>28</v>
       </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="2:5">
-      <c r="B14" s="8">
-        <v>12</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="C55" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="2:9">
+      <c r="B56" s="9">
         <v>29</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="C56" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="2:9">
+      <c r="B57" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="2:9">
+      <c r="B58" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="2:9">
+      <c r="B59" s="9">
         <v>30</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="C59" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="2:9">
+      <c r="B60" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="2:9">
+      <c r="B61" s="9">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="2:5">
-      <c r="B15" s="8">
-        <v>13</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="C61" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="2:9">
+      <c r="B62" s="9">
         <v>32</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="C62" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="2:9">
+      <c r="B63" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="2:9">
+      <c r="B64" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="2:9">
+      <c r="B65" s="9">
         <v>33</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="C65" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="2:9">
+      <c r="B66" s="9">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="2:5">
-      <c r="B16" s="8">
-        <v>14</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="C66" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="2:9">
+      <c r="B67" s="9">
         <v>35</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="C67" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="2:9">
+      <c r="B68" s="9">
         <v>36</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="C68" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="2:9">
+      <c r="B69" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="2:9">
+      <c r="B70" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="2:9">
+      <c r="B71" s="9">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="2:5">
-      <c r="B17" s="8">
-        <v>15</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="C71" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="2:9">
+      <c r="B72" s="9">
         <v>38</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="C72" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="2:9">
+      <c r="B73" s="9">
         <v>39</v>
       </c>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="2:5">
-      <c r="B18" s="8">
-        <v>16</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="C73" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="2:9">
+      <c r="B74" s="9">
         <v>40</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="C74" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="2:9">
+      <c r="B75" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="2:9">
+      <c r="B76" s="9">
         <v>41</v>
       </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" customHeight="1" spans="2:5">
-      <c r="B19" s="8">
-        <v>17</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="2:5">
-      <c r="B20" s="8">
-        <v>18</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customHeight="1" spans="2:5">
-      <c r="B21" s="8">
-        <v>19</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="C76" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="2:9">
+      <c r="B77" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="2:9">
+      <c r="B78" s="9">
         <v>42</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="C78" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="2:9">
+      <c r="B79" s="9">
         <v>43</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customHeight="1" spans="2:5">
-      <c r="B22" s="8">
-        <v>20</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="C79" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="2:9">
+      <c r="B80" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="2:9">
+      <c r="B81" s="9">
         <v>44</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="C81" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="2:9">
+      <c r="B82" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="2:9">
+      <c r="B83" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="2:9">
+      <c r="B84" s="9">
         <v>45</v>
       </c>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="2:5">
-      <c r="B23" s="8">
-        <v>21</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="C84" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="2:9">
+      <c r="B85" s="9">
         <v>46</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="C85" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="2:9">
+      <c r="B86" s="9">
         <v>47</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="C86" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="2:9">
+      <c r="B87" s="13">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="2:5">
-      <c r="B24" s="8">
-        <v>22</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="2:5">
-      <c r="B25" s="8">
-        <v>23</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" customHeight="1" spans="2:5">
-      <c r="B26" s="8">
-        <v>24</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" customHeight="1" spans="2:5">
-      <c r="B27" s="8">
-        <v>25</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customHeight="1" spans="2:5">
-      <c r="B28" s="8">
-        <v>26</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" customHeight="1" spans="2:5">
-      <c r="B29" s="8">
-        <v>27</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="2:5">
-      <c r="B30" s="8">
-        <v>28</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" customHeight="1" spans="2:5">
-      <c r="B31" s="8">
-        <v>29</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="2:5">
-      <c r="B32" s="11">
-        <v>30</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32" s="7"/>
+      <c r="C87" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I87" s="16" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
